--- a/backend/data/financials_by_company/1KRN.MI.xlsx
+++ b/backend/data/financials_by_company/1KRN.MI.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV5"/>
+  <dimension ref="A1:AV6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -662,58 +662,58 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>70692</v>
+        <v>4654.755726</v>
       </c>
       <c r="C2" t="n">
-        <v>0.274</v>
+        <v>0.202381</v>
       </c>
       <c r="D2" t="n">
-        <v>564534000</v>
+        <v>324500000</v>
       </c>
       <c r="E2" t="n">
-        <v>258000</v>
+        <v>23000</v>
       </c>
       <c r="F2" t="n">
-        <v>258000</v>
+        <v>23000</v>
       </c>
       <c r="G2" t="n">
-        <v>276919000</v>
+        <v>141366000</v>
       </c>
       <c r="H2" t="n">
-        <v>168430000</v>
+        <v>141738000</v>
       </c>
       <c r="I2" t="n">
-        <v>2576438000</v>
+        <v>1769539000</v>
       </c>
       <c r="J2" t="n">
-        <v>564792000</v>
+        <v>324523000</v>
       </c>
       <c r="K2" t="n">
-        <v>396362000</v>
+        <v>182785000</v>
       </c>
       <c r="L2" t="n">
-        <v>7691000</v>
+        <v>4366000</v>
       </c>
       <c r="M2" t="n">
-        <v>14739000</v>
+        <v>5525000</v>
       </c>
       <c r="N2" t="n">
-        <v>22430000</v>
+        <v>9891000</v>
       </c>
       <c r="O2" t="n">
-        <v>276731692</v>
+        <v>141347654.755726</v>
       </c>
       <c r="P2" t="n">
-        <v>276919000</v>
+        <v>141366000</v>
       </c>
       <c r="Q2" t="n">
-        <v>4918518000</v>
+        <v>3457273000</v>
       </c>
       <c r="R2" t="n">
-        <v>18721000</v>
+        <v>5492000</v>
       </c>
       <c r="S2" t="n">
         <v>31593072</v>
@@ -722,144 +722,144 @@
         <v>31593072</v>
       </c>
       <c r="U2" t="n">
-        <v>8.77</v>
+        <v>4.47</v>
       </c>
       <c r="V2" t="n">
-        <v>8.77</v>
+        <v>4.47</v>
       </c>
       <c r="W2" t="n">
-        <v>276919000</v>
+        <v>141366000</v>
       </c>
       <c r="X2" t="n">
-        <v>276919000</v>
+        <v>141366000</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>276919000</v>
+        <v>141366000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-293000</v>
+        <v>-20000</v>
       </c>
       <c r="AB2" t="n">
-        <v>277212000</v>
+        <v>141386000</v>
       </c>
       <c r="AC2" t="n">
-        <v>277212000</v>
+        <v>141386000</v>
       </c>
       <c r="AD2" t="n">
-        <v>104411000</v>
+        <v>35874000</v>
       </c>
       <c r="AE2" t="n">
-        <v>381623000</v>
+        <v>177260000</v>
       </c>
       <c r="AF2" t="n">
-        <v>258000</v>
+        <v>23000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-258000</v>
+        <v>-23000</v>
       </c>
       <c r="AH2" t="n">
-        <v>7691000</v>
+        <v>4366000</v>
       </c>
       <c r="AI2" t="n">
-        <v>14739000</v>
+        <v>5525000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>22430000</v>
+        <v>9891000</v>
       </c>
       <c r="AK2" t="n">
-        <v>375039000</v>
+        <v>177183000</v>
       </c>
       <c r="AL2" t="n">
-        <v>2342080000</v>
+        <v>1687734000</v>
       </c>
       <c r="AM2" t="n">
-        <v>462329000</v>
+        <v>284786000</v>
       </c>
       <c r="AN2" t="n">
-        <v>168430000</v>
+        <v>141738000</v>
       </c>
       <c r="AO2" t="n">
-        <v>168430000</v>
+        <v>141738000</v>
       </c>
       <c r="AP2" t="n">
-        <v>151440000</v>
+        <v>129994000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>151440000</v>
+        <v>129994000</v>
       </c>
       <c r="AR2" t="n">
-        <v>18721000</v>
+        <v>5492000</v>
       </c>
       <c r="AS2" t="n">
-        <v>2717119000</v>
+        <v>1864917000</v>
       </c>
       <c r="AT2" t="n">
-        <v>2576438000</v>
+        <v>1769539000</v>
       </c>
       <c r="AU2" t="n">
-        <v>5293557000</v>
+        <v>3634456000</v>
       </c>
       <c r="AV2" t="n">
-        <v>5293557000</v>
+        <v>3634456000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>2576654</v>
+        <v>280070.526511</v>
       </c>
       <c r="C3" t="n">
-        <v>0.277</v>
+        <v>0.227146</v>
       </c>
       <c r="D3" t="n">
-        <v>483989000</v>
+        <v>387088000</v>
       </c>
       <c r="E3" t="n">
-        <v>9302000</v>
+        <v>1233000</v>
       </c>
       <c r="F3" t="n">
-        <v>9302000</v>
+        <v>1233000</v>
       </c>
       <c r="G3" t="n">
-        <v>224511000</v>
+        <v>187025000</v>
       </c>
       <c r="H3" t="n">
-        <v>166324000</v>
+        <v>142901000</v>
       </c>
       <c r="I3" t="n">
-        <v>2384555000</v>
+        <v>2065733000</v>
       </c>
       <c r="J3" t="n">
-        <v>493291000</v>
+        <v>388321000</v>
       </c>
       <c r="K3" t="n">
-        <v>326967000</v>
+        <v>245420000</v>
       </c>
       <c r="L3" t="n">
-        <v>15787000</v>
+        <v>8600000</v>
       </c>
       <c r="M3" t="n">
-        <v>16471000</v>
+        <v>3355000</v>
       </c>
       <c r="N3" t="n">
-        <v>32258000</v>
+        <v>11955000</v>
       </c>
       <c r="O3" t="n">
-        <v>217785654</v>
+        <v>186072070.526511</v>
       </c>
       <c r="P3" t="n">
-        <v>224511000</v>
+        <v>187025000</v>
       </c>
       <c r="Q3" t="n">
-        <v>4440286000</v>
+        <v>3957910000</v>
       </c>
       <c r="R3" t="n">
-        <v>12426000</v>
+        <v>6962000</v>
       </c>
       <c r="S3" t="n">
         <v>31593072</v>
@@ -868,144 +868,144 @@
         <v>31593072</v>
       </c>
       <c r="U3" t="n">
-        <v>7.11</v>
+        <v>5.92</v>
       </c>
       <c r="V3" t="n">
-        <v>7.11</v>
+        <v>5.92</v>
       </c>
       <c r="W3" t="n">
-        <v>224511000</v>
+        <v>187025000</v>
       </c>
       <c r="X3" t="n">
-        <v>224511000</v>
+        <v>187025000</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>224511000</v>
+        <v>187025000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-39000</v>
+        <v>-56000</v>
       </c>
       <c r="AB3" t="n">
-        <v>224550000</v>
+        <v>187081000</v>
       </c>
       <c r="AC3" t="n">
-        <v>224550000</v>
+        <v>187081000</v>
       </c>
       <c r="AD3" t="n">
-        <v>85946000</v>
+        <v>54984000</v>
       </c>
       <c r="AE3" t="n">
-        <v>310496000</v>
+        <v>242065000</v>
       </c>
       <c r="AF3" t="n">
-        <v>9302000</v>
+        <v>1233000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-9302000</v>
+        <v>-1233000</v>
       </c>
       <c r="AH3" t="n">
-        <v>15787000</v>
+        <v>8600000</v>
       </c>
       <c r="AI3" t="n">
-        <v>16471000</v>
+        <v>3355000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>32258000</v>
+        <v>11955000</v>
       </c>
       <c r="AK3" t="n">
-        <v>280390000</v>
+        <v>251429000</v>
       </c>
       <c r="AL3" t="n">
-        <v>2055731000</v>
+        <v>1892177000</v>
       </c>
       <c r="AM3" t="n">
-        <v>379772000</v>
+        <v>350764000</v>
       </c>
       <c r="AN3" t="n">
-        <v>166324000</v>
+        <v>142901000</v>
       </c>
       <c r="AO3" t="n">
-        <v>166324000</v>
+        <v>142901000</v>
       </c>
       <c r="AP3" t="n">
-        <v>141457000</v>
+        <v>156203000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>141457000</v>
+        <v>156203000</v>
       </c>
       <c r="AR3" t="n">
-        <v>12426000</v>
+        <v>6962000</v>
       </c>
       <c r="AS3" t="n">
-        <v>2336121000</v>
+        <v>2143606000</v>
       </c>
       <c r="AT3" t="n">
-        <v>2384555000</v>
+        <v>2065733000</v>
       </c>
       <c r="AU3" t="n">
-        <v>4720676000</v>
+        <v>4209339000</v>
       </c>
       <c r="AV3" t="n">
-        <v>4720676000</v>
+        <v>4209339000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>280070.526511</v>
+        <v>2576654</v>
       </c>
       <c r="C4" t="n">
-        <v>0.227146</v>
+        <v>0.277</v>
       </c>
       <c r="D4" t="n">
-        <v>387088000</v>
+        <v>483989000</v>
       </c>
       <c r="E4" t="n">
-        <v>1233000</v>
+        <v>9302000</v>
       </c>
       <c r="F4" t="n">
-        <v>1233000</v>
+        <v>9302000</v>
       </c>
       <c r="G4" t="n">
-        <v>187025000</v>
+        <v>224511000</v>
       </c>
       <c r="H4" t="n">
-        <v>142901000</v>
+        <v>166324000</v>
       </c>
       <c r="I4" t="n">
-        <v>2065733000</v>
+        <v>2384555000</v>
       </c>
       <c r="J4" t="n">
-        <v>388321000</v>
+        <v>493291000</v>
       </c>
       <c r="K4" t="n">
-        <v>245420000</v>
+        <v>326967000</v>
       </c>
       <c r="L4" t="n">
-        <v>8600000</v>
+        <v>15787000</v>
       </c>
       <c r="M4" t="n">
-        <v>3355000</v>
+        <v>16471000</v>
       </c>
       <c r="N4" t="n">
-        <v>11955000</v>
+        <v>32258000</v>
       </c>
       <c r="O4" t="n">
-        <v>186072070.526511</v>
+        <v>217785654</v>
       </c>
       <c r="P4" t="n">
-        <v>187025000</v>
+        <v>224511000</v>
       </c>
       <c r="Q4" t="n">
-        <v>3957910000</v>
+        <v>4440286000</v>
       </c>
       <c r="R4" t="n">
-        <v>6962000</v>
+        <v>12426000</v>
       </c>
       <c r="S4" t="n">
         <v>31593072</v>
@@ -1014,144 +1014,144 @@
         <v>31593072</v>
       </c>
       <c r="U4" t="n">
-        <v>5.92</v>
+        <v>7.11</v>
       </c>
       <c r="V4" t="n">
-        <v>5.92</v>
+        <v>7.11</v>
       </c>
       <c r="W4" t="n">
-        <v>187025000</v>
+        <v>224511000</v>
       </c>
       <c r="X4" t="n">
-        <v>187025000</v>
+        <v>224511000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>187025000</v>
+        <v>224511000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-56000</v>
+        <v>-39000</v>
       </c>
       <c r="AB4" t="n">
-        <v>187081000</v>
+        <v>224550000</v>
       </c>
       <c r="AC4" t="n">
-        <v>187081000</v>
+        <v>224550000</v>
       </c>
       <c r="AD4" t="n">
-        <v>54984000</v>
+        <v>85946000</v>
       </c>
       <c r="AE4" t="n">
-        <v>242065000</v>
+        <v>310496000</v>
       </c>
       <c r="AF4" t="n">
-        <v>1233000</v>
+        <v>9302000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-1233000</v>
+        <v>-9302000</v>
       </c>
       <c r="AH4" t="n">
-        <v>8600000</v>
+        <v>15787000</v>
       </c>
       <c r="AI4" t="n">
-        <v>3355000</v>
+        <v>16471000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>11955000</v>
+        <v>32258000</v>
       </c>
       <c r="AK4" t="n">
-        <v>251429000</v>
+        <v>280390000</v>
       </c>
       <c r="AL4" t="n">
-        <v>1892177000</v>
+        <v>2055731000</v>
       </c>
       <c r="AM4" t="n">
-        <v>350764000</v>
+        <v>379772000</v>
       </c>
       <c r="AN4" t="n">
-        <v>142901000</v>
+        <v>166324000</v>
       </c>
       <c r="AO4" t="n">
-        <v>142901000</v>
+        <v>166324000</v>
       </c>
       <c r="AP4" t="n">
-        <v>156203000</v>
+        <v>141457000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>156203000</v>
+        <v>141457000</v>
       </c>
       <c r="AR4" t="n">
-        <v>6962000</v>
+        <v>12426000</v>
       </c>
       <c r="AS4" t="n">
-        <v>2143606000</v>
+        <v>2336121000</v>
       </c>
       <c r="AT4" t="n">
-        <v>2065733000</v>
+        <v>2384555000</v>
       </c>
       <c r="AU4" t="n">
-        <v>4209339000</v>
+        <v>4720676000</v>
       </c>
       <c r="AV4" t="n">
-        <v>4209339000</v>
+        <v>4720676000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>4654.755726</v>
+        <v>70692</v>
       </c>
       <c r="C5" t="n">
-        <v>0.202381</v>
+        <v>0.274</v>
       </c>
       <c r="D5" t="n">
-        <v>324500000</v>
+        <v>564534000</v>
       </c>
       <c r="E5" t="n">
-        <v>23000</v>
+        <v>258000</v>
       </c>
       <c r="F5" t="n">
-        <v>23000</v>
+        <v>258000</v>
       </c>
       <c r="G5" t="n">
-        <v>141366000</v>
+        <v>276919000</v>
       </c>
       <c r="H5" t="n">
-        <v>141738000</v>
+        <v>168430000</v>
       </c>
       <c r="I5" t="n">
-        <v>1769539000</v>
+        <v>2576438000</v>
       </c>
       <c r="J5" t="n">
-        <v>324523000</v>
+        <v>564792000</v>
       </c>
       <c r="K5" t="n">
-        <v>182785000</v>
+        <v>396362000</v>
       </c>
       <c r="L5" t="n">
-        <v>4366000</v>
+        <v>7691000</v>
       </c>
       <c r="M5" t="n">
-        <v>5525000</v>
+        <v>14739000</v>
       </c>
       <c r="N5" t="n">
-        <v>9891000</v>
+        <v>22430000</v>
       </c>
       <c r="O5" t="n">
-        <v>141347654.755726</v>
+        <v>276731692</v>
       </c>
       <c r="P5" t="n">
-        <v>141366000</v>
+        <v>276919000</v>
       </c>
       <c r="Q5" t="n">
-        <v>3457273000</v>
+        <v>4918518000</v>
       </c>
       <c r="R5" t="n">
-        <v>5492000</v>
+        <v>18721000</v>
       </c>
       <c r="S5" t="n">
         <v>31593072</v>
@@ -1160,88 +1160,234 @@
         <v>31593072</v>
       </c>
       <c r="U5" t="n">
-        <v>4.47</v>
+        <v>8.77</v>
       </c>
       <c r="V5" t="n">
-        <v>4.47</v>
+        <v>8.77</v>
       </c>
       <c r="W5" t="n">
-        <v>141366000</v>
+        <v>276919000</v>
       </c>
       <c r="X5" t="n">
-        <v>141366000</v>
+        <v>276919000</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>141366000</v>
+        <v>276919000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-20000</v>
+        <v>-293000</v>
       </c>
       <c r="AB5" t="n">
-        <v>141386000</v>
+        <v>277212000</v>
       </c>
       <c r="AC5" t="n">
-        <v>141386000</v>
+        <v>277212000</v>
       </c>
       <c r="AD5" t="n">
-        <v>35874000</v>
+        <v>104411000</v>
       </c>
       <c r="AE5" t="n">
-        <v>177260000</v>
+        <v>381623000</v>
       </c>
       <c r="AF5" t="n">
-        <v>23000</v>
+        <v>258000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-23000</v>
+        <v>-258000</v>
       </c>
       <c r="AH5" t="n">
-        <v>4366000</v>
+        <v>7691000</v>
       </c>
       <c r="AI5" t="n">
-        <v>5525000</v>
+        <v>14739000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>9891000</v>
+        <v>22430000</v>
       </c>
       <c r="AK5" t="n">
-        <v>177183000</v>
+        <v>375039000</v>
       </c>
       <c r="AL5" t="n">
-        <v>1687734000</v>
+        <v>2342080000</v>
       </c>
       <c r="AM5" t="n">
-        <v>284786000</v>
+        <v>462329000</v>
       </c>
       <c r="AN5" t="n">
-        <v>141738000</v>
+        <v>168430000</v>
       </c>
       <c r="AO5" t="n">
-        <v>141738000</v>
+        <v>168430000</v>
       </c>
       <c r="AP5" t="n">
-        <v>129994000</v>
+        <v>151440000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>129994000</v>
+        <v>151440000</v>
       </c>
       <c r="AR5" t="n">
-        <v>5492000</v>
+        <v>18721000</v>
       </c>
       <c r="AS5" t="n">
-        <v>1864917000</v>
+        <v>2717119000</v>
       </c>
       <c r="AT5" t="n">
-        <v>1769539000</v>
+        <v>2576438000</v>
       </c>
       <c r="AU5" t="n">
-        <v>3634456000</v>
+        <v>5293557000</v>
       </c>
       <c r="AV5" t="n">
-        <v>3634456000</v>
+        <v>5293557000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>411230</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="D6" t="n">
+        <v>618493000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1394000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1394000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>298688000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>185276000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2702890000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>619887000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>434611000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3082000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>10477000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>13559000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>297705230</v>
+      </c>
+      <c r="P6" t="n">
+        <v>298688000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>5284225000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>22567000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>31593072</v>
+      </c>
+      <c r="T6" t="n">
+        <v>31593072</v>
+      </c>
+      <c r="U6" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="V6" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="W6" t="n">
+        <v>298688000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>298688000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>298688000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-478000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>299166000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>299166000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>124968000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>424134000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1394000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-1394000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>3082000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>10477000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>13559000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>379544000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>2581335000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>534348000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>185276000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>185276000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>167470000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>167470000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>22567000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>2960879000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>2702890000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>5663769000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>5663769000</v>
       </c>
     </row>
   </sheetData>
@@ -1255,7 +1401,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ5"/>
+  <dimension ref="A1:BQ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1602,214 +1748,82 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>31593072</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31593072</v>
-      </c>
-      <c r="D2" t="n">
-        <v>136623000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1334689000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1924325000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>805571000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1334689000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>134004000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1921706000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1923045000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1921537000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>-169000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1921706000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>-2000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1518995000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>141724000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2827932000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>435005000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>266000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>172651000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>725000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2981000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>28388000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>94550000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>93211000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1339000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>95952000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>2392927000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>51470000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>42073000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>40793000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1280000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>11970000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>191493000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>878720000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>76526000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>802194000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>4749469000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>1550971000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>7440000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>67831000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>16747000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>5777000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>587017000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>358538000</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>228479000</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>852210000</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>-953954000</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>1806164000</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>55449000</v>
-      </c>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="n">
-        <v>857291000</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>893424000</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>3198498000</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>180305000</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>664752000</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>6657000</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>140160000</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>119076000</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>398859000</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>1094433000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>7663000</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>808862000</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>442483000</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>442483000</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>442483000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="n">
+        <v>708981000</v>
+      </c>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr"/>
+      <c r="BO2" t="inlineStr"/>
+      <c r="BP2" t="inlineStr"/>
+      <c r="BQ2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>31593072</v>
@@ -1818,41 +1832,41 @@
         <v>31593072</v>
       </c>
       <c r="D3" t="n">
-        <v>139740000</v>
+        <v>110929000</v>
       </c>
       <c r="E3" t="n">
-        <v>1254695000</v>
+        <v>1249225000</v>
       </c>
       <c r="F3" t="n">
-        <v>1719150000</v>
+        <v>1603574000</v>
       </c>
       <c r="G3" t="n">
-        <v>797754000</v>
+        <v>808729000</v>
       </c>
       <c r="H3" t="n">
-        <v>1254695000</v>
+        <v>1249225000</v>
       </c>
       <c r="I3" t="n">
-        <v>135975000</v>
+        <v>105929000</v>
       </c>
       <c r="J3" t="n">
-        <v>1715385000</v>
+        <v>1598574000</v>
       </c>
       <c r="K3" t="n">
-        <v>1717906000</v>
+        <v>1603574000</v>
       </c>
       <c r="L3" t="n">
-        <v>1714923000</v>
+        <v>1598073000</v>
       </c>
       <c r="M3" t="n">
-        <v>-462000</v>
+        <v>-501000</v>
       </c>
       <c r="N3" t="n">
-        <v>1715385000</v>
+        <v>1598574000</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>1312158000</v>
+        <v>1143172000</v>
       </c>
       <c r="Q3" t="n">
         <v>141724000</v>
@@ -1864,159 +1878,159 @@
         <v>40000000</v>
       </c>
       <c r="T3" t="n">
-        <v>2762186000</v>
+        <v>2573093000</v>
       </c>
       <c r="U3" t="n">
-        <v>410229000</v>
+        <v>374845000</v>
       </c>
       <c r="V3" t="n">
-        <v>248000</v>
+        <v>2973000</v>
       </c>
       <c r="W3" t="n">
-        <v>178444000</v>
+        <v>166584000</v>
       </c>
       <c r="X3" t="n">
-        <v>943000</v>
+        <v>1075000</v>
       </c>
       <c r="Y3" t="n">
-        <v>3612000</v>
+        <v>4979000</v>
       </c>
       <c r="Z3" t="n">
-        <v>13539000</v>
+        <v>4992000</v>
       </c>
       <c r="AA3" t="n">
-        <v>102704000</v>
+        <v>87083000</v>
       </c>
       <c r="AB3" t="n">
-        <v>100183000</v>
+        <v>82083000</v>
       </c>
       <c r="AC3" t="n">
-        <v>2521000</v>
+        <v>5000000</v>
       </c>
       <c r="AD3" t="n">
-        <v>81472000</v>
+        <v>80305000</v>
       </c>
       <c r="AE3" t="n">
-        <v>2351957000</v>
+        <v>2198248000</v>
       </c>
       <c r="AF3" t="n">
-        <v>42633000</v>
+        <v>50918000</v>
       </c>
       <c r="AG3" t="n">
-        <v>37036000</v>
+        <v>23846000</v>
       </c>
       <c r="AH3" t="n">
-        <v>35792000</v>
+        <v>23846000</v>
       </c>
       <c r="AI3" t="n">
-        <v>1244000</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>11033000</v>
+        <v>12432000</v>
       </c>
       <c r="AK3" t="n">
-        <v>148069000</v>
+        <v>161945000</v>
       </c>
       <c r="AL3" t="n">
-        <v>784030000</v>
+        <v>750034000</v>
       </c>
       <c r="AM3" t="n">
-        <v>60866000</v>
+        <v>65845000</v>
       </c>
       <c r="AN3" t="n">
-        <v>723164000</v>
+        <v>684189000</v>
       </c>
       <c r="AO3" t="n">
-        <v>4477109000</v>
+        <v>4171166000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1327398000</v>
+        <v>1164189000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>6055000</v>
+        <v>11368000</v>
       </c>
       <c r="AR3" t="n">
-        <v>60544000</v>
+        <v>59857000</v>
       </c>
       <c r="AS3" t="n">
-        <v>17686000</v>
+        <v>18605000</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>2364000</v>
       </c>
       <c r="AU3" t="n">
-        <v>460690000</v>
+        <v>349349000</v>
       </c>
       <c r="AV3" t="n">
-        <v>277637000</v>
+        <v>214912000</v>
       </c>
       <c r="AW3" t="n">
-        <v>183053000</v>
+        <v>134437000</v>
       </c>
       <c r="AX3" t="n">
-        <v>762577000</v>
+        <v>693663000</v>
       </c>
       <c r="AY3" t="n">
-        <v>-898168000</v>
+        <v>-856874000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>762577000</v>
+        <v>693663000</v>
       </c>
       <c r="BA3" t="n">
-        <v>43611000</v>
+        <v>27551000</v>
       </c>
       <c r="BB3" t="n">
-        <v>762577000</v>
+        <v>693663000</v>
       </c>
       <c r="BC3" t="n">
-        <v>788622000</v>
+        <v>749302000</v>
       </c>
       <c r="BD3" t="n">
-        <v>828512000</v>
+        <v>773684000</v>
       </c>
       <c r="BE3" t="n">
-        <v>3149711000</v>
+        <v>3006977000</v>
       </c>
       <c r="BF3" t="n">
-        <v>220045000</v>
+        <v>190015000</v>
       </c>
       <c r="BG3" t="n">
-        <v>641374000</v>
+        <v>589445000</v>
       </c>
       <c r="BH3" t="n">
-        <v>7132000</v>
+        <v>5784000</v>
       </c>
       <c r="BI3" t="n">
-        <v>99102000</v>
+        <v>95694000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>98564000</v>
+        <v>92990000</v>
       </c>
       <c r="BK3" t="n">
-        <v>436576000</v>
+        <v>394977000</v>
       </c>
       <c r="BL3" t="n">
-        <v>1056319000</v>
+        <v>727555000</v>
       </c>
       <c r="BM3" t="n">
-        <v>4901000</v>
+        <v>5217000</v>
       </c>
       <c r="BN3" t="n">
-        <v>778708000</v>
+        <v>820243000</v>
       </c>
       <c r="BO3" t="n">
-        <v>448364000</v>
+        <v>674502000</v>
       </c>
       <c r="BP3" t="n">
-        <v>448364000</v>
+        <v>674502000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>448364000</v>
+        <v>674502000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>31593072</v>
@@ -2025,41 +2039,41 @@
         <v>31593072</v>
       </c>
       <c r="D4" t="n">
-        <v>110929000</v>
+        <v>139740000</v>
       </c>
       <c r="E4" t="n">
-        <v>1249225000</v>
+        <v>1254695000</v>
       </c>
       <c r="F4" t="n">
-        <v>1603574000</v>
+        <v>1719150000</v>
       </c>
       <c r="G4" t="n">
-        <v>808729000</v>
+        <v>797754000</v>
       </c>
       <c r="H4" t="n">
-        <v>1249225000</v>
+        <v>1254695000</v>
       </c>
       <c r="I4" t="n">
-        <v>105929000</v>
+        <v>135975000</v>
       </c>
       <c r="J4" t="n">
-        <v>1598574000</v>
+        <v>1715385000</v>
       </c>
       <c r="K4" t="n">
-        <v>1603574000</v>
+        <v>1717906000</v>
       </c>
       <c r="L4" t="n">
-        <v>1598073000</v>
+        <v>1714923000</v>
       </c>
       <c r="M4" t="n">
-        <v>-501000</v>
+        <v>-462000</v>
       </c>
       <c r="N4" t="n">
-        <v>1598574000</v>
+        <v>1715385000</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>1143172000</v>
+        <v>1312158000</v>
       </c>
       <c r="Q4" t="n">
         <v>141724000</v>
@@ -2071,159 +2085,159 @@
         <v>40000000</v>
       </c>
       <c r="T4" t="n">
-        <v>2573093000</v>
+        <v>2762186000</v>
       </c>
       <c r="U4" t="n">
-        <v>374845000</v>
+        <v>410229000</v>
       </c>
       <c r="V4" t="n">
-        <v>2973000</v>
+        <v>248000</v>
       </c>
       <c r="W4" t="n">
-        <v>166584000</v>
+        <v>178444000</v>
       </c>
       <c r="X4" t="n">
-        <v>1075000</v>
+        <v>943000</v>
       </c>
       <c r="Y4" t="n">
-        <v>4979000</v>
+        <v>3612000</v>
       </c>
       <c r="Z4" t="n">
-        <v>4992000</v>
+        <v>13539000</v>
       </c>
       <c r="AA4" t="n">
-        <v>87083000</v>
+        <v>102704000</v>
       </c>
       <c r="AB4" t="n">
-        <v>82083000</v>
+        <v>100183000</v>
       </c>
       <c r="AC4" t="n">
-        <v>5000000</v>
+        <v>2521000</v>
       </c>
       <c r="AD4" t="n">
-        <v>80305000</v>
+        <v>81472000</v>
       </c>
       <c r="AE4" t="n">
-        <v>2198248000</v>
+        <v>2351957000</v>
       </c>
       <c r="AF4" t="n">
-        <v>50918000</v>
+        <v>42633000</v>
       </c>
       <c r="AG4" t="n">
-        <v>23846000</v>
+        <v>37036000</v>
       </c>
       <c r="AH4" t="n">
-        <v>23846000</v>
+        <v>35792000</v>
       </c>
       <c r="AI4" t="n">
+        <v>1244000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>11033000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>148069000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>784030000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>60866000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>723164000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>4477109000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1327398000</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>6055000</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>60544000</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>17686000</v>
+      </c>
+      <c r="AT4" t="n">
         <v>0</v>
       </c>
-      <c r="AJ4" t="n">
-        <v>12432000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>161945000</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>750034000</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>65845000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>684189000</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>4171166000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1164189000</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>11368000</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>59857000</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>18605000</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>2364000</v>
-      </c>
       <c r="AU4" t="n">
-        <v>349349000</v>
+        <v>460690000</v>
       </c>
       <c r="AV4" t="n">
-        <v>214912000</v>
+        <v>277637000</v>
       </c>
       <c r="AW4" t="n">
-        <v>134437000</v>
+        <v>183053000</v>
       </c>
       <c r="AX4" t="n">
-        <v>693663000</v>
+        <v>762577000</v>
       </c>
       <c r="AY4" t="n">
-        <v>-856874000</v>
+        <v>-898168000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>693663000</v>
+        <v>762577000</v>
       </c>
       <c r="BA4" t="n">
-        <v>27551000</v>
+        <v>43611000</v>
       </c>
       <c r="BB4" t="n">
-        <v>693663000</v>
+        <v>762577000</v>
       </c>
       <c r="BC4" t="n">
-        <v>749302000</v>
+        <v>788622000</v>
       </c>
       <c r="BD4" t="n">
-        <v>773684000</v>
+        <v>828512000</v>
       </c>
       <c r="BE4" t="n">
-        <v>3006977000</v>
+        <v>3149711000</v>
       </c>
       <c r="BF4" t="n">
-        <v>190015000</v>
+        <v>220045000</v>
       </c>
       <c r="BG4" t="n">
-        <v>589445000</v>
+        <v>641374000</v>
       </c>
       <c r="BH4" t="n">
-        <v>5784000</v>
+        <v>7132000</v>
       </c>
       <c r="BI4" t="n">
-        <v>95694000</v>
+        <v>99102000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>92990000</v>
+        <v>98564000</v>
       </c>
       <c r="BK4" t="n">
-        <v>394977000</v>
+        <v>436576000</v>
       </c>
       <c r="BL4" t="n">
-        <v>727555000</v>
+        <v>1056319000</v>
       </c>
       <c r="BM4" t="n">
-        <v>5217000</v>
+        <v>4901000</v>
       </c>
       <c r="BN4" t="n">
-        <v>820243000</v>
+        <v>778708000</v>
       </c>
       <c r="BO4" t="n">
-        <v>674502000</v>
+        <v>448364000</v>
       </c>
       <c r="BP4" t="n">
-        <v>674502000</v>
+        <v>448364000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>674502000</v>
+        <v>448364000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>31593072</v>
@@ -2232,41 +2246,43 @@
         <v>31593072</v>
       </c>
       <c r="D5" t="n">
-        <v>102522000</v>
+        <v>136623000</v>
       </c>
       <c r="E5" t="n">
-        <v>1088980000</v>
+        <v>1334689000</v>
       </c>
       <c r="F5" t="n">
-        <v>1397238000</v>
+        <v>1924325000</v>
       </c>
       <c r="G5" t="n">
-        <v>693190000</v>
+        <v>805571000</v>
       </c>
       <c r="H5" t="n">
-        <v>1088980000</v>
+        <v>1334689000</v>
       </c>
       <c r="I5" t="n">
-        <v>97424000</v>
+        <v>134004000</v>
       </c>
       <c r="J5" t="n">
-        <v>1392140000</v>
+        <v>1921706000</v>
       </c>
       <c r="K5" t="n">
-        <v>1397238000</v>
+        <v>1923045000</v>
       </c>
       <c r="L5" t="n">
-        <v>1391583000</v>
+        <v>1921537000</v>
       </c>
       <c r="M5" t="n">
-        <v>-557000</v>
+        <v>-169000</v>
       </c>
       <c r="N5" t="n">
-        <v>1392140000</v>
-      </c>
-      <c r="O5" t="inlineStr"/>
+        <v>1921706000</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-2000</v>
+      </c>
       <c r="P5" t="n">
-        <v>1000813000</v>
+        <v>1518995000</v>
       </c>
       <c r="Q5" t="n">
         <v>141724000</v>
@@ -2278,154 +2294,357 @@
         <v>40000000</v>
       </c>
       <c r="T5" t="n">
-        <v>2103253000</v>
+        <v>2827932000</v>
       </c>
       <c r="U5" t="n">
-        <v>434411000</v>
+        <v>435005000</v>
       </c>
       <c r="V5" t="n">
-        <v>8311000</v>
+        <v>266000</v>
       </c>
       <c r="W5" t="n">
-        <v>251156000</v>
+        <v>172651000</v>
       </c>
       <c r="X5" t="n">
-        <v>1393000</v>
+        <v>725000</v>
       </c>
       <c r="Y5" t="n">
-        <v>4641000</v>
+        <v>2981000</v>
       </c>
       <c r="Z5" t="n">
-        <v>5293000</v>
+        <v>28388000</v>
       </c>
       <c r="AA5" t="n">
-        <v>72896000</v>
+        <v>94550000</v>
       </c>
       <c r="AB5" t="n">
-        <v>67798000</v>
+        <v>93211000</v>
       </c>
       <c r="AC5" t="n">
-        <v>5098000</v>
+        <v>1339000</v>
       </c>
       <c r="AD5" t="n">
-        <v>78819000</v>
+        <v>95952000</v>
       </c>
       <c r="AE5" t="n">
-        <v>1668842000</v>
+        <v>2392927000</v>
       </c>
       <c r="AF5" t="n">
-        <v>49760000</v>
+        <v>51470000</v>
       </c>
       <c r="AG5" t="n">
-        <v>29626000</v>
+        <v>42073000</v>
       </c>
       <c r="AH5" t="n">
-        <v>29626000</v>
+        <v>40793000</v>
       </c>
       <c r="AI5" t="n">
+        <v>1280000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>11970000</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>191493000</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>878720000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>76526000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>802194000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>4749469000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1550971000</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>7440000</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>67831000</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>16747000</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>5777000</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>587017000</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>358538000</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>228479000</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>852210000</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>-953954000</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>852210000</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>55338000</v>
+      </c>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="n">
+        <v>294942000</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>501930000</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>3198498000</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>180305000</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>664752000</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>6657000</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>140160000</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>119076000</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>398859000</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1094433000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>7663000</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>808862000</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>442483000</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>442483000</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>442483000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>31593072</v>
+      </c>
+      <c r="C6" t="n">
+        <v>31593072</v>
+      </c>
+      <c r="D6" t="n">
+        <v>148844000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1527822000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2129652000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>944733000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1527822000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>147578000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2128386000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2128386000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2128695000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>309000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2128386000</v>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>1734871000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>141724000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2913429000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>453030000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>761000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>159539000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>528000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>3212000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>57300000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>103682000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>103682000</v>
+      </c>
+      <c r="AC6" t="n">
         <v>0</v>
       </c>
-      <c r="AJ5" t="n">
-        <v>8487000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>164523000</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>578015000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>62874000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>515141000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>3494836000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1132804000</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>11676000</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>75177000</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>28846000</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>2357000</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>303160000</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>197768000</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>105392000</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>667009000</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>-821130000</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>1488139000</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>24406000</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>708981000</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>708981000</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>754752000</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>2362032000</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>195785000</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>433604000</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>7659000</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>74773000</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>69747000</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>281425000</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>593969000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>11977000</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>743326000</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>383371000</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>383371000</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>383371000</v>
+      <c r="AD6" t="n">
+        <v>97580000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2460399000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>27829000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>45162000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>43896000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1266000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>12684000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>223617000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>953334000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>85078000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>868256000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>5042124000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1636992000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>8475000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>63154000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>15489000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>6545000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>600564000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>365654000</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>234910000</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>921576000</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>-1011956000</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1933532000</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>99568000</v>
+      </c>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="n">
+        <v>904550000</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>929414000</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>3405132000</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>191509000</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>677375000</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>4332000</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>155251000</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>112230000</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>405562000</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1075975000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>11232000</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>899553000</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>549488000</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>549488000</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>549488000</v>
       </c>
     </row>
   </sheetData>
@@ -2439,7 +2658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT5"/>
+  <dimension ref="A1:AT6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2671,532 +2890,584 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>271032000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-1247000</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="n">
-        <v>-181138000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>442483000</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="n">
-        <v>448364000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-4063000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-1818000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-114995000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-69505000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>-1247000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>-1247000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>-1247000</v>
-      </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="n">
-        <v>-338993000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>8899000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>4797000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2290000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2290000</v>
-      </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="n">
-        <v>-179355000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>15970000</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="n">
+        <v>-30420000</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="n">
-        <v>-179355000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-59659000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>752000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-60411000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-115965000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>4762000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-120727000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>452170000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-92672000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-6531000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>8357000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>-77168000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>18471000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>20697000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>-6779000</v>
-      </c>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="n">
-        <v>168430000</v>
-      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="n">
+        <v>3533000</v>
+      </c>
+      <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="n">
-        <v>168430000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>-258000</v>
-      </c>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="n">
-        <v>381623000</v>
-      </c>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="n">
+        <v>-23000</v>
+      </c>
+      <c r="AT2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-25042000</v>
+        <v>360542000</v>
       </c>
       <c r="C3" t="n">
-        <v>-1235000</v>
+        <v>-98000</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-162664000</v>
+        <v>-118157000</v>
       </c>
       <c r="F3" t="n">
-        <v>448364000</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
+        <v>674502000</v>
+      </c>
+      <c r="G3" t="n">
+        <v>298000</v>
+      </c>
       <c r="H3" t="n">
-        <v>674502000</v>
+        <v>383371000</v>
       </c>
       <c r="I3" t="n">
-        <v>-30754000</v>
+        <v>-328000</v>
       </c>
       <c r="J3" t="n">
-        <v>-195384000</v>
+        <v>291161000</v>
       </c>
       <c r="K3" t="n">
-        <v>-94096000</v>
+        <v>-79786000</v>
       </c>
       <c r="L3" t="n">
-        <v>-55288000</v>
+        <v>-44230000</v>
       </c>
       <c r="M3" t="n">
-        <v>-1235000</v>
+        <v>-98000</v>
       </c>
       <c r="N3" t="n">
-        <v>-1235000</v>
+        <v>-98000</v>
       </c>
       <c r="O3" t="n">
-        <v>-1235000</v>
+        <v>-98000</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-238910000</v>
+        <v>-107752000</v>
       </c>
       <c r="R3" t="n">
-        <v>15935000</v>
+        <v>8607000</v>
       </c>
       <c r="S3" t="n">
-        <v>3723000</v>
+        <v>3052000</v>
       </c>
       <c r="T3" t="n">
-        <v>2692000</v>
+        <v>28860000</v>
       </c>
       <c r="U3" t="n">
-        <v>2692000</v>
+        <v>29235000</v>
       </c>
       <c r="V3" t="n">
+        <v>-375000</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-34346000</v>
+      </c>
+      <c r="X3" t="n">
         <v>0</v>
       </c>
-      <c r="W3" t="n">
-        <v>-112856000</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2000000</v>
-      </c>
       <c r="Y3" t="n">
-        <v>-114856000</v>
+        <v>-34346000</v>
       </c>
       <c r="Z3" t="n">
-        <v>-45323000</v>
+        <v>-45751000</v>
       </c>
       <c r="AA3" t="n">
-        <v>66000</v>
+        <v>238000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-45389000</v>
+        <v>-45989000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-103081000</v>
+        <v>-68174000</v>
       </c>
       <c r="AD3" t="n">
-        <v>14194000</v>
+        <v>3994000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-117275000</v>
+        <v>-72168000</v>
       </c>
       <c r="AF3" t="n">
-        <v>137622000</v>
+        <v>478699000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-76754000</v>
+        <v>-61710000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-9314000</v>
+        <v>-1991000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-249159000</v>
+        <v>156232000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>204802000</v>
+        <v>437458000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-55864000</v>
+        <v>-163402000</v>
       </c>
       <c r="AL3" t="n">
-        <v>-365641000</v>
+        <v>-163515000</v>
       </c>
       <c r="AM3" t="n">
-        <v>5331000</v>
+        <v>2435000</v>
       </c>
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="n">
-        <v>166324000</v>
-      </c>
-      <c r="AP3" t="inlineStr"/>
+        <v>142901000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>46890000</v>
+      </c>
       <c r="AQ3" t="n">
-        <v>166324000</v>
+        <v>96011000</v>
       </c>
       <c r="AR3" t="n">
-        <v>-9302000</v>
-      </c>
-      <c r="AS3" t="inlineStr"/>
+        <v>-1233000</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>-1233000</v>
+      </c>
       <c r="AT3" t="n">
-        <v>310496000</v>
+        <v>242065000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>360542000</v>
+        <v>-25042000</v>
       </c>
       <c r="C4" t="n">
-        <v>-98000</v>
+        <v>-1235000</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-118157000</v>
+        <v>-162664000</v>
       </c>
       <c r="F4" t="n">
+        <v>448364000</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="n">
         <v>674502000</v>
       </c>
-      <c r="G4" t="n">
-        <v>298000</v>
-      </c>
-      <c r="H4" t="n">
-        <v>383371000</v>
-      </c>
       <c r="I4" t="n">
-        <v>-328000</v>
+        <v>-30754000</v>
       </c>
       <c r="J4" t="n">
-        <v>291161000</v>
+        <v>-195384000</v>
       </c>
       <c r="K4" t="n">
-        <v>-79786000</v>
+        <v>-94096000</v>
       </c>
       <c r="L4" t="n">
-        <v>-44230000</v>
+        <v>-55288000</v>
       </c>
       <c r="M4" t="n">
-        <v>-98000</v>
+        <v>-1235000</v>
       </c>
       <c r="N4" t="n">
-        <v>-98000</v>
+        <v>-1235000</v>
       </c>
       <c r="O4" t="n">
-        <v>-98000</v>
+        <v>-1235000</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-107752000</v>
+        <v>-238910000</v>
       </c>
       <c r="R4" t="n">
-        <v>8607000</v>
+        <v>15935000</v>
       </c>
       <c r="S4" t="n">
-        <v>3052000</v>
+        <v>3723000</v>
       </c>
       <c r="T4" t="n">
-        <v>28860000</v>
+        <v>2692000</v>
       </c>
       <c r="U4" t="n">
-        <v>29235000</v>
+        <v>2692000</v>
       </c>
       <c r="V4" t="n">
-        <v>-375000</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-34346000</v>
+        <v>-112856000</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="Y4" t="n">
-        <v>-34346000</v>
+        <v>-114856000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-45751000</v>
+        <v>-45323000</v>
       </c>
       <c r="AA4" t="n">
-        <v>238000</v>
+        <v>66000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-45989000</v>
+        <v>-45389000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-68174000</v>
+        <v>-103081000</v>
       </c>
       <c r="AD4" t="n">
-        <v>3994000</v>
+        <v>14194000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-72168000</v>
+        <v>-117275000</v>
       </c>
       <c r="AF4" t="n">
-        <v>478699000</v>
+        <v>137622000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-61710000</v>
+        <v>-76754000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-1991000</v>
+        <v>-9314000</v>
       </c>
       <c r="AI4" t="n">
-        <v>156232000</v>
+        <v>-249159000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>437458000</v>
+        <v>204802000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-163402000</v>
+        <v>-55864000</v>
       </c>
       <c r="AL4" t="n">
-        <v>-163515000</v>
+        <v>-365641000</v>
       </c>
       <c r="AM4" t="n">
-        <v>2435000</v>
+        <v>5331000</v>
       </c>
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="n">
-        <v>142901000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>46890000</v>
-      </c>
+        <v>166324000</v>
+      </c>
+      <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="n">
-        <v>96011000</v>
+        <v>166324000</v>
       </c>
       <c r="AR4" t="n">
-        <v>-1233000</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>-1233000</v>
-      </c>
+        <v>-9302000</v>
+      </c>
+      <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
-        <v>242065000</v>
+        <v>310496000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>230968000</v>
+        <v>271032000</v>
       </c>
       <c r="C5" t="n">
-        <v>-26966000</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
+        <v>-1247000</v>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>-104890000</v>
+        <v>-181138000</v>
       </c>
       <c r="F5" t="n">
-        <v>383371000</v>
-      </c>
-      <c r="G5" t="n">
-        <v>15970000</v>
-      </c>
+        <v>442483000</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>216988000</v>
+        <v>448364000</v>
       </c>
       <c r="I5" t="n">
-        <v>8050000</v>
+        <v>-4063000</v>
       </c>
       <c r="J5" t="n">
-        <v>142363000</v>
+        <v>-1818000</v>
       </c>
       <c r="K5" t="n">
-        <v>-60891000</v>
+        <v>-114995000</v>
       </c>
       <c r="L5" t="n">
-        <v>-1896000</v>
+        <v>-69505000</v>
       </c>
       <c r="M5" t="n">
-        <v>-26966000</v>
+        <v>-1247000</v>
       </c>
       <c r="N5" t="n">
-        <v>-26966000</v>
+        <v>-1247000</v>
       </c>
       <c r="O5" t="n">
-        <v>-26966000</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
+        <v>-1247000</v>
+      </c>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>-132604000</v>
+        <v>-338993000</v>
       </c>
       <c r="R5" t="n">
-        <v>7402000</v>
+        <v>8899000</v>
       </c>
       <c r="S5" t="n">
-        <v>2032000</v>
+        <v>4797000</v>
       </c>
       <c r="T5" t="n">
-        <v>-28685000</v>
+        <v>2290000</v>
       </c>
       <c r="U5" t="n">
-        <v>1735000</v>
-      </c>
-      <c r="V5" t="n">
-        <v>-30420000</v>
-      </c>
+        <v>2290000</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>-11150000</v>
+        <v>-179355000</v>
       </c>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="n">
-        <v>-11150000</v>
+        <v>-179355000</v>
       </c>
       <c r="Z5" t="n">
-        <v>-43422000</v>
+        <v>-59659000</v>
       </c>
       <c r="AA5" t="n">
-        <v>230000</v>
+        <v>752000</v>
       </c>
       <c r="AB5" t="n">
-        <v>-43652000</v>
+        <v>-60411000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-58781000</v>
+        <v>-115965000</v>
       </c>
       <c r="AD5" t="n">
-        <v>2457000</v>
+        <v>4762000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-61238000</v>
+        <v>-120727000</v>
       </c>
       <c r="AF5" t="n">
-        <v>335858000</v>
+        <v>452170000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-54301000</v>
+        <v>-92672000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-2805000</v>
+        <v>-6531000</v>
       </c>
       <c r="AI5" t="n">
-        <v>65537000</v>
+        <v>8357000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>256805000</v>
+        <v>-77168000</v>
       </c>
       <c r="AK5" t="n">
-        <v>-72348000</v>
+        <v>18471000</v>
       </c>
       <c r="AL5" t="n">
-        <v>-122453000</v>
+        <v>20697000</v>
       </c>
       <c r="AM5" t="n">
-        <v>8452000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>3533000</v>
-      </c>
+        <v>-6779000</v>
+      </c>
+      <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="n">
-        <v>141738000</v>
+        <v>168430000</v>
       </c>
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="n">
-        <v>141738000</v>
+        <v>168430000</v>
       </c>
       <c r="AR5" t="n">
-        <v>-23000</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>-23000</v>
-      </c>
+        <v>-258000</v>
+      </c>
+      <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
-        <v>177260000</v>
+        <v>381623000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>261203000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-3478000</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>-185126000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>549488000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2789000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>442483000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-15395000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>119611000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-128113000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-82142000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-3478000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-3478000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-3478000</v>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="n">
+        <v>-198605000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>9578000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3231000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1153000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1153000</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>-35213000</v>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="n">
+        <v>-35213000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-53652000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1236000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-54888000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-123702000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>6536000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-130238000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>446329000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-111845000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-7267000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-55539000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>97838000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-31581000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>-182233000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>12964000</v>
+      </c>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="n">
+        <v>185276000</v>
+      </c>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="n">
+        <v>185276000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-1394000</v>
+      </c>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="n">
+        <v>424134000</v>
       </c>
     </row>
   </sheetData>
@@ -3210,7 +3481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EU2"/>
+  <dimension ref="A1:ET2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3326,645 +3597,640 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>compensationAsOfEpochDate</t>
+          <t>executiveTeam</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>executiveTeam</t>
+          <t>maxAge</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>maxAge</t>
+          <t>priceHint</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>priceHint</t>
+          <t>previousClose</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>previousClose</t>
+          <t>open</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>dayLow</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>dayLow</t>
+          <t>dayHigh</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>dayHigh</t>
+          <t>regularMarketPreviousClose</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>regularMarketPreviousClose</t>
+          <t>regularMarketOpen</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>regularMarketOpen</t>
+          <t>regularMarketDayLow</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>regularMarketDayLow</t>
+          <t>regularMarketDayHigh</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>regularMarketDayHigh</t>
+          <t>dividendRate</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>dividendRate</t>
+          <t>dividendYield</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>dividendYield</t>
+          <t>exDividendDate</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
         <is>
-          <t>exDividendDate</t>
+          <t>payoutRatio</t>
         </is>
       </c>
       <c r="AL1" t="inlineStr">
         <is>
-          <t>payoutRatio</t>
+          <t>beta</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>beta</t>
+          <t>trailingPE</t>
         </is>
       </c>
       <c r="AN1" t="inlineStr">
         <is>
-          <t>trailingPE</t>
+          <t>volume</t>
         </is>
       </c>
       <c r="AO1" t="inlineStr">
         <is>
-          <t>volume</t>
+          <t>regularMarketVolume</t>
         </is>
       </c>
       <c r="AP1" t="inlineStr">
         <is>
-          <t>regularMarketVolume</t>
+          <t>averageVolume</t>
         </is>
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
-          <t>averageVolume</t>
+          <t>averageVolume10days</t>
         </is>
       </c>
       <c r="AR1" t="inlineStr">
         <is>
-          <t>averageVolume10days</t>
+          <t>averageDailyVolume10Day</t>
         </is>
       </c>
       <c r="AS1" t="inlineStr">
         <is>
-          <t>averageDailyVolume10Day</t>
+          <t>bid</t>
         </is>
       </c>
       <c r="AT1" t="inlineStr">
         <is>
-          <t>bid</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AU1" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>marketCap</t>
         </is>
       </c>
       <c r="AV1" t="inlineStr">
         <is>
-          <t>marketCap</t>
+          <t>nonDilutedMarketCap</t>
         </is>
       </c>
       <c r="AW1" t="inlineStr">
         <is>
-          <t>nonDilutedMarketCap</t>
+          <t>fiftyTwoWeekLow</t>
         </is>
       </c>
       <c r="AX1" t="inlineStr">
         <is>
-          <t>fiftyTwoWeekLow</t>
+          <t>fiftyTwoWeekHigh</t>
         </is>
       </c>
       <c r="AY1" t="inlineStr">
         <is>
-          <t>fiftyTwoWeekHigh</t>
+          <t>allTimeHigh</t>
         </is>
       </c>
       <c r="AZ1" t="inlineStr">
         <is>
-          <t>allTimeHigh</t>
+          <t>allTimeLow</t>
         </is>
       </c>
       <c r="BA1" t="inlineStr">
         <is>
-          <t>allTimeLow</t>
+          <t>priceToSalesTrailing12Months</t>
         </is>
       </c>
       <c r="BB1" t="inlineStr">
         <is>
-          <t>priceToSalesTrailing12Months</t>
+          <t>fiftyDayAverage</t>
         </is>
       </c>
       <c r="BC1" t="inlineStr">
         <is>
-          <t>fiftyDayAverage</t>
+          <t>twoHundredDayAverage</t>
         </is>
       </c>
       <c r="BD1" t="inlineStr">
         <is>
-          <t>twoHundredDayAverage</t>
+          <t>trailingAnnualDividendRate</t>
         </is>
       </c>
       <c r="BE1" t="inlineStr">
         <is>
-          <t>trailingAnnualDividendRate</t>
+          <t>trailingAnnualDividendYield</t>
         </is>
       </c>
       <c r="BF1" t="inlineStr">
         <is>
-          <t>trailingAnnualDividendYield</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="BG1" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>tradeable</t>
         </is>
       </c>
       <c r="BH1" t="inlineStr">
         <is>
-          <t>tradeable</t>
+          <t>enterpriseValue</t>
         </is>
       </c>
       <c r="BI1" t="inlineStr">
         <is>
-          <t>enterpriseValue</t>
+          <t>profitMargins</t>
         </is>
       </c>
       <c r="BJ1" t="inlineStr">
         <is>
-          <t>profitMargins</t>
+          <t>floatShares</t>
         </is>
       </c>
       <c r="BK1" t="inlineStr">
         <is>
-          <t>floatShares</t>
+          <t>sharesOutstanding</t>
         </is>
       </c>
       <c r="BL1" t="inlineStr">
         <is>
-          <t>sharesOutstanding</t>
+          <t>heldPercentInsiders</t>
         </is>
       </c>
       <c r="BM1" t="inlineStr">
         <is>
-          <t>heldPercentInsiders</t>
+          <t>heldPercentInstitutions</t>
         </is>
       </c>
       <c r="BN1" t="inlineStr">
         <is>
-          <t>heldPercentInstitutions</t>
+          <t>impliedSharesOutstanding</t>
         </is>
       </c>
       <c r="BO1" t="inlineStr">
         <is>
-          <t>impliedSharesOutstanding</t>
+          <t>bookValue</t>
         </is>
       </c>
       <c r="BP1" t="inlineStr">
         <is>
-          <t>bookValue</t>
+          <t>priceToBook</t>
         </is>
       </c>
       <c r="BQ1" t="inlineStr">
         <is>
-          <t>priceToBook</t>
+          <t>lastFiscalYearEnd</t>
         </is>
       </c>
       <c r="BR1" t="inlineStr">
         <is>
-          <t>lastFiscalYearEnd</t>
+          <t>nextFiscalYearEnd</t>
         </is>
       </c>
       <c r="BS1" t="inlineStr">
         <is>
-          <t>nextFiscalYearEnd</t>
+          <t>mostRecentQuarter</t>
         </is>
       </c>
       <c r="BT1" t="inlineStr">
         <is>
-          <t>mostRecentQuarter</t>
+          <t>earningsQuarterlyGrowth</t>
         </is>
       </c>
       <c r="BU1" t="inlineStr">
         <is>
-          <t>earningsQuarterlyGrowth</t>
+          <t>netIncomeToCommon</t>
         </is>
       </c>
       <c r="BV1" t="inlineStr">
         <is>
-          <t>netIncomeToCommon</t>
+          <t>trailingEps</t>
         </is>
       </c>
       <c r="BW1" t="inlineStr">
         <is>
-          <t>trailingEps</t>
+          <t>enterpriseToRevenue</t>
         </is>
       </c>
       <c r="BX1" t="inlineStr">
         <is>
-          <t>enterpriseToRevenue</t>
+          <t>enterpriseToEbitda</t>
         </is>
       </c>
       <c r="BY1" t="inlineStr">
         <is>
-          <t>enterpriseToEbitda</t>
+          <t>52WeekChange</t>
         </is>
       </c>
       <c r="BZ1" t="inlineStr">
         <is>
-          <t>52WeekChange</t>
+          <t>SandP52WeekChange</t>
         </is>
       </c>
       <c r="CA1" t="inlineStr">
         <is>
-          <t>SandP52WeekChange</t>
+          <t>lastDividendValue</t>
         </is>
       </c>
       <c r="CB1" t="inlineStr">
         <is>
-          <t>lastDividendValue</t>
+          <t>lastDividendDate</t>
         </is>
       </c>
       <c r="CC1" t="inlineStr">
         <is>
-          <t>lastDividendDate</t>
+          <t>quoteType</t>
         </is>
       </c>
       <c r="CD1" t="inlineStr">
         <is>
-          <t>quoteType</t>
+          <t>currentPrice</t>
         </is>
       </c>
       <c r="CE1" t="inlineStr">
         <is>
-          <t>currentPrice</t>
+          <t>recommendationKey</t>
         </is>
       </c>
       <c r="CF1" t="inlineStr">
         <is>
-          <t>recommendationKey</t>
+          <t>totalCash</t>
         </is>
       </c>
       <c r="CG1" t="inlineStr">
         <is>
-          <t>totalCash</t>
+          <t>totalCashPerShare</t>
         </is>
       </c>
       <c r="CH1" t="inlineStr">
         <is>
-          <t>totalCashPerShare</t>
+          <t>ebitda</t>
         </is>
       </c>
       <c r="CI1" t="inlineStr">
         <is>
-          <t>ebitda</t>
+          <t>totalDebt</t>
         </is>
       </c>
       <c r="CJ1" t="inlineStr">
         <is>
-          <t>totalDebt</t>
+          <t>quickRatio</t>
         </is>
       </c>
       <c r="CK1" t="inlineStr">
         <is>
-          <t>quickRatio</t>
+          <t>currentRatio</t>
         </is>
       </c>
       <c r="CL1" t="inlineStr">
         <is>
-          <t>currentRatio</t>
+          <t>totalRevenue</t>
         </is>
       </c>
       <c r="CM1" t="inlineStr">
         <is>
-          <t>totalRevenue</t>
+          <t>debtToEquity</t>
         </is>
       </c>
       <c r="CN1" t="inlineStr">
         <is>
-          <t>debtToEquity</t>
+          <t>revenuePerShare</t>
         </is>
       </c>
       <c r="CO1" t="inlineStr">
         <is>
-          <t>revenuePerShare</t>
+          <t>returnOnAssets</t>
         </is>
       </c>
       <c r="CP1" t="inlineStr">
         <is>
-          <t>returnOnAssets</t>
+          <t>returnOnEquity</t>
         </is>
       </c>
       <c r="CQ1" t="inlineStr">
         <is>
-          <t>returnOnEquity</t>
+          <t>grossProfits</t>
         </is>
       </c>
       <c r="CR1" t="inlineStr">
         <is>
-          <t>grossProfits</t>
+          <t>freeCashflow</t>
         </is>
       </c>
       <c r="CS1" t="inlineStr">
         <is>
-          <t>freeCashflow</t>
+          <t>operatingCashflow</t>
         </is>
       </c>
       <c r="CT1" t="inlineStr">
         <is>
-          <t>operatingCashflow</t>
+          <t>earningsGrowth</t>
         </is>
       </c>
       <c r="CU1" t="inlineStr">
         <is>
-          <t>earningsGrowth</t>
+          <t>revenueGrowth</t>
         </is>
       </c>
       <c r="CV1" t="inlineStr">
         <is>
-          <t>revenueGrowth</t>
+          <t>grossMargins</t>
         </is>
       </c>
       <c r="CW1" t="inlineStr">
         <is>
-          <t>grossMargins</t>
+          <t>ebitdaMargins</t>
         </is>
       </c>
       <c r="CX1" t="inlineStr">
         <is>
-          <t>ebitdaMargins</t>
+          <t>operatingMargins</t>
         </is>
       </c>
       <c r="CY1" t="inlineStr">
         <is>
-          <t>operatingMargins</t>
+          <t>financialCurrency</t>
         </is>
       </c>
       <c r="CZ1" t="inlineStr">
         <is>
-          <t>financialCurrency</t>
+          <t>symbol</t>
         </is>
       </c>
       <c r="DA1" t="inlineStr">
         <is>
-          <t>symbol</t>
+          <t>language</t>
         </is>
       </c>
       <c r="DB1" t="inlineStr">
         <is>
-          <t>language</t>
+          <t>region</t>
         </is>
       </c>
       <c r="DC1" t="inlineStr">
         <is>
-          <t>region</t>
+          <t>typeDisp</t>
         </is>
       </c>
       <c r="DD1" t="inlineStr">
         <is>
-          <t>typeDisp</t>
+          <t>quoteSourceName</t>
         </is>
       </c>
       <c r="DE1" t="inlineStr">
         <is>
-          <t>quoteSourceName</t>
+          <t>triggerable</t>
         </is>
       </c>
       <c r="DF1" t="inlineStr">
         <is>
-          <t>triggerable</t>
+          <t>customPriceAlertConfidence</t>
         </is>
       </c>
       <c r="DG1" t="inlineStr">
         <is>
-          <t>customPriceAlertConfidence</t>
+          <t>shortName</t>
         </is>
       </c>
       <c r="DH1" t="inlineStr">
         <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>earningsTimestamp</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>earningsCallTimestampStart</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>earningsCallTimestampEnd</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="EA1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="EB1" t="inlineStr">
+      <c r="EN1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="EC1" t="inlineStr">
+      <c r="EO1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="ED1" t="inlineStr">
+      <c r="EP1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="EE1" t="inlineStr">
+      <c r="EQ1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="EF1" t="inlineStr">
+      <c r="ER1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="EG1" t="inlineStr">
+      <c r="ES1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="ER1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="ES1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
       <c r="ET1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="EU1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -3981,10 +4247,8 @@
           <t>Neutraubling</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>93073</t>
-        </is>
+      <c r="C2" t="n">
+        <v>93073</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -4046,7 +4310,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Christoph  Klenk', 'age': 62, 'title': 'Chairman of Executive Board &amp; CEO', 'yearBorn': 1963, 'fiscalYear': 2024, 'totalPay': 1500000, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Uta  Anders', 'age': 55, 'title': 'CFO &amp; Member of Executive Board', 'yearBorn': 1970, 'fiscalYear': 2024, 'totalPay': 1010000, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Thomas  Ricker', 'age': 57, 'title': 'Chief Sales Officer &amp; Member of Executive Board', 'yearBorn': 1968, 'fiscalYear': 2024, 'totalPay': 1017000, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Markus  Tischer', 'age': 57, 'title': 'Member of Executive Board', 'yearBorn': 1968, 'fiscalYear': 2024, 'totalPay': 1013000, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Ralf  Goldbrunner', 'age': 55, 'title': 'COO &amp; Member of Executive Board', 'yearBorn': 1970, 'fiscalYear': 2024, 'totalPay': 879000, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Olaf  Scholz', 'title': 'Head of Investor Relations, Treasury and M&amp;A', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Roland  Pokorny', 'title': 'Head of Corporate Communications', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ingrid  Reuschl', 'title': 'Head of Public Relations', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -4065,24 +4329,24 @@
         <v>6</v>
       </c>
       <c r="V2" t="n">
-        <v>1780272000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1735603200</v>
-      </c>
-      <c r="X2" t="inlineStr">
+        <v>1780531200</v>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
+      <c r="X2" t="n">
+        <v>86400</v>
+      </c>
       <c r="Y2" t="n">
-        <v>86400</v>
+        <v>2</v>
       </c>
       <c r="Z2" t="n">
-        <v>2</v>
+        <v>119.8</v>
       </c>
       <c r="AA2" t="n">
-        <v>119.8</v>
+        <v>120.2</v>
       </c>
       <c r="AB2" t="n">
         <v>120.2</v>
@@ -4091,10 +4355,10 @@
         <v>120.2</v>
       </c>
       <c r="AD2" t="n">
+        <v>119.8</v>
+      </c>
+      <c r="AE2" t="n">
         <v>120.2</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>119.8</v>
       </c>
       <c r="AF2" t="n">
         <v>120.2</v>
@@ -4103,399 +4367,396 @@
         <v>120.2</v>
       </c>
       <c r="AH2" t="n">
-        <v>120.2</v>
+        <v>2.8</v>
       </c>
       <c r="AI2" t="n">
-        <v>2.8</v>
+        <v>2.29</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2.29</v>
+        <v>1781049600</v>
       </c>
       <c r="AK2" t="n">
-        <v>1781049600</v>
+        <v>0.282</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.28350002</v>
+        <v>0.93</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.949</v>
+        <v>12.4593725</v>
       </c>
       <c r="AN2" t="n">
-        <v>12.5408945</v>
+        <v>3</v>
       </c>
       <c r="AO2" t="n">
         <v>3</v>
       </c>
       <c r="AP2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
       </c>
       <c r="AS2" t="n">
+        <v>116.4</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>117</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>3633203200</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>3721663881</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>146.2</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>149</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0.63856256</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>122.288</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>132.286</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>0.023372287</v>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="BG2" t="b">
         <v>0</v>
       </c>
-      <c r="AT2" t="n">
-        <v>116.4</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>117</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>3633203200</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>3664796352</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>118.2</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>146.2</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>149</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>118.2</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>0.63856256</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>126.864</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>132.845</v>
-      </c>
-      <c r="BE2" t="n">
+      <c r="BH2" t="n">
+        <v>3105854464</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>0.051230002</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>13363869</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>31593072</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>0.577</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>0.20191</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>31593072</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>69.791</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>1.647777</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>1767139200</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>1798675200</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>1774915200</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>-0.095</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>291488000</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>0.546</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>6.295</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>-0.15491009</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>0.24487448</v>
+      </c>
+      <c r="CA2" t="n">
         <v>2.8</v>
       </c>
-      <c r="BF2" t="n">
-        <v>0.023372287</v>
-      </c>
-      <c r="BG2" t="inlineStr">
+      <c r="CB2" t="n">
+        <v>1781049600</v>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="CD2" t="n">
+        <v>115</v>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="CF2" t="n">
+        <v>524100000</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>16.589</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>493399008</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>47300000</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>5689658880</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>2.145</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>180.056</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>0.04696</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>0.13934</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>3002278912</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>28770376</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>284728992</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>-0.096</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>-0.025</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>0.52766997</v>
+      </c>
+      <c r="CW2" t="n">
+        <v>0.08672000000000001</v>
+      </c>
+      <c r="CX2" t="n">
+        <v>0.04202</v>
+      </c>
+      <c r="CY2" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="BH2" t="b">
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>1KRN.MI</t>
+        </is>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>en-US</t>
+        </is>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>Delayed Quote</t>
+        </is>
+      </c>
+      <c r="DE2" t="b">
         <v>0</v>
       </c>
-      <c r="BI2" t="n">
-        <v>3219589376</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0.051230002</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>13363869</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>31593072</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>0.577</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>0.20292</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>31593072</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>69.791</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>1.647777</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>1767139200</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>1798675200</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>1774915200</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>-0.095</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>291488000</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>9.17</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>0.5659999999999999</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>6.525</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>-0.15491009</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>0.27449715</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="CC2" t="n">
-        <v>1781049600</v>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>EQUITY</t>
-        </is>
-      </c>
-      <c r="CE2" t="n">
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>Krones AG</t>
+        </is>
+      </c>
+      <c r="DH2" t="n">
+        <v>-4.00668</v>
+      </c>
+      <c r="DI2" t="n">
         <v>115</v>
       </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="CG2" t="n">
-        <v>524100000</v>
-      </c>
-      <c r="CH2" t="n">
-        <v>16.589</v>
-      </c>
-      <c r="CI2" t="n">
-        <v>493399008</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>47300000</v>
-      </c>
-      <c r="CK2" t="n">
-        <v>1.031</v>
-      </c>
-      <c r="CL2" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="CM2" t="n">
-        <v>5689658880</v>
-      </c>
-      <c r="CN2" t="n">
-        <v>2.145</v>
-      </c>
-      <c r="CO2" t="n">
-        <v>180.056</v>
-      </c>
-      <c r="CP2" t="n">
-        <v>0.04696</v>
-      </c>
-      <c r="CQ2" t="n">
-        <v>0.13934</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>3002278912</v>
-      </c>
-      <c r="CS2" t="n">
-        <v>28770376</v>
-      </c>
-      <c r="CT2" t="n">
-        <v>284728992</v>
-      </c>
-      <c r="CU2" t="n">
-        <v>-0.096</v>
-      </c>
-      <c r="CV2" t="n">
-        <v>-0.025</v>
-      </c>
-      <c r="CW2" t="n">
-        <v>0.52766997</v>
-      </c>
-      <c r="CX2" t="n">
-        <v>0.08672000000000001</v>
-      </c>
-      <c r="CY2" t="n">
-        <v>0.04202</v>
-      </c>
-      <c r="CZ2" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="DA2" t="inlineStr">
-        <is>
-          <t>1KRN.MI</t>
-        </is>
-      </c>
-      <c r="DB2" t="inlineStr">
-        <is>
-          <t>en-US</t>
-        </is>
-      </c>
-      <c r="DC2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="DD2" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="DE2" t="inlineStr">
-        <is>
-          <t>Delayed Quote</t>
-        </is>
-      </c>
-      <c r="DF2" t="b">
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DK2" t="n">
+        <v>1776086747</v>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>finmb_876993</t>
+        </is>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>Europe/Rome</t>
+        </is>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>CEST</t>
+        </is>
+      </c>
+      <c r="DP2" t="n">
+        <v>7200000</v>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>it_market</t>
+        </is>
+      </c>
+      <c r="DR2" t="b">
         <v>0</v>
       </c>
-      <c r="DG2" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="DH2" t="b">
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="DT2" t="b">
         <v>0</v>
       </c>
-      <c r="DI2" t="n">
+      <c r="DU2" t="n">
         <v>1747119600000</v>
       </c>
-      <c r="DJ2" t="n">
+      <c r="DV2" t="n">
         <v>-4.800003</v>
       </c>
-      <c r="DK2" t="inlineStr">
+      <c r="DW2" t="inlineStr">
         <is>
           <t>120.2 - 120.2</t>
         </is>
       </c>
-      <c r="DL2" t="inlineStr">
+      <c r="DX2" t="inlineStr">
         <is>
           <t>Milan</t>
         </is>
       </c>
-      <c r="DM2" t="n">
+      <c r="DY2" t="n">
         <v>1</v>
       </c>
-      <c r="DN2" t="n">
+      <c r="DZ2" t="n">
         <v>-3.199997</v>
       </c>
-      <c r="DO2" t="n">
+      <c r="EA2" t="n">
         <v>-0.027072733</v>
       </c>
-      <c r="DP2" t="inlineStr">
+      <c r="EB2" t="inlineStr">
         <is>
           <t>118.2 - 146.2</t>
         </is>
       </c>
-      <c r="DQ2" t="n">
+      <c r="EC2" t="n">
         <v>-31.199997</v>
       </c>
-      <c r="DR2" t="n">
+      <c r="ED2" t="n">
         <v>-0.21340628</v>
       </c>
-      <c r="DS2" t="n">
+      <c r="EE2" t="n">
         <v>-15.491009</v>
       </c>
-      <c r="DT2" t="n">
+      <c r="EF2" t="n">
         <v>1785339000</v>
       </c>
-      <c r="DU2" t="n">
+      <c r="EG2" t="n">
         <v>1785339000</v>
       </c>
-      <c r="DV2" t="n">
+      <c r="EH2" t="n">
         <v>1785339000</v>
       </c>
-      <c r="DW2" t="n">
+      <c r="EI2" t="n">
         <v>1785339000</v>
       </c>
-      <c r="DX2" t="n">
+      <c r="EJ2" t="n">
         <v>1785339000</v>
       </c>
-      <c r="DY2" t="b">
+      <c r="EK2" t="b">
         <v>0</v>
       </c>
-      <c r="DZ2" t="n">
-        <v>9.17</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>-11.863998</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>-0.09351745</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>-17.845001</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>-0.13432948</v>
-      </c>
-      <c r="EE2" t="n">
+      <c r="EL2" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>-7.288002</v>
+      </c>
+      <c r="EN2" t="n">
+        <v>-0.059597034</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>-17.285995</v>
+      </c>
+      <c r="EP2" t="n">
+        <v>-0.1306714</v>
+      </c>
+      <c r="EQ2" t="n">
         <v>20</v>
       </c>
-      <c r="EF2" t="n">
+      <c r="ER2" t="n">
         <v>15</v>
       </c>
-      <c r="EG2" t="b">
+      <c r="ES2" t="b">
         <v>0</v>
       </c>
-      <c r="EH2" t="inlineStr">
-        <is>
-          <t>[{'header': 'Dividend', 'message': '1KRN.MI announced a cash dividend of EUR 2.80 with an ex-date of Jun. 10, 2026', 'meta': {'eventType': 'DIVIDEND', 'dateEpochMs': 1781042400000, 'amount': '2.80'}}]</t>
-        </is>
-      </c>
-      <c r="EI2" t="n">
-        <v>1776086747</v>
-      </c>
-      <c r="EJ2" t="inlineStr">
-        <is>
-          <t>Krones AG</t>
-        </is>
-      </c>
-      <c r="EK2" t="n">
-        <v>-4.00668</v>
-      </c>
-      <c r="EL2" t="n">
-        <v>115</v>
-      </c>
-      <c r="EM2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="EN2" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="EO2" t="inlineStr">
-        <is>
-          <t>finmb_876993</t>
-        </is>
-      </c>
-      <c r="EP2" t="inlineStr">
-        <is>
-          <t>Europe/Rome</t>
-        </is>
-      </c>
-      <c r="EQ2" t="inlineStr">
-        <is>
-          <t>CEST</t>
-        </is>
-      </c>
-      <c r="ER2" t="n">
-        <v>7200000</v>
-      </c>
-      <c r="ES2" t="inlineStr">
-        <is>
-          <t>it_market</t>
-        </is>
-      </c>
-      <c r="ET2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EU2" t="inlineStr"/>
+      <c r="ET2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
